--- a/tables/datas/common/#Skill-技能表.xlsx
+++ b/tables/datas/common/#Skill-技能表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -636,7 +636,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1,1,1.5</t>
+          <t>1,1,1.5,0</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -677,7 +677,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1,1,0.8|2,1,0</t>
+          <t>1,1,0.8,0|4,1,0,10</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1,1,0.6</t>
+          <t>1,1,0.6,0</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -759,7 +759,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1,2,1.5</t>
+          <t>1,2,1.5,0</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -800,7 +800,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1,2,1.0</t>
+          <t>1,2,1.0,0|4,2,0,6</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -841,7 +841,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1,2,0.8</t>
+          <t>1,2,0.8,0</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -882,7 +882,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1,2,1.0</t>
+          <t>1,2,1.0,0</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -923,7 +923,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1,2,2.0</t>
+          <t>1,2,2.0,0</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -964,7 +964,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1,2,0.8</t>
+          <t>1,2,0.8,0</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1,1,1.2</t>
+          <t>1,1,1.2,0</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1,1,0.5</t>
+          <t>1,1,0.5,0</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -1087,10 +1087,502 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1,1,1.0|2,1,0</t>
+          <t>1,1,1.0,0|4,1,0,10</t>
         </is>
       </c>
       <c r="L15" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>20</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>战吼</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F16" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>10</v>
+      </c>
+      <c r="I16" t="n">
+        <v>20</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>AllAlliesInRange</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>4,1,0,3</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>21</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>石肤术</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F17" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>15</v>
+      </c>
+      <c r="I17" t="n">
+        <v>10</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>4,1,0,5</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>22</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>毒雾</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F18" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>8</v>
+      </c>
+      <c r="I18" t="n">
+        <v>25</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>AllEnemiesInRange</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>4,2,0,1</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>23</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>冰冻术</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>10</v>
+      </c>
+      <c r="I19" t="n">
+        <v>20</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>SingleEnemy</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>1,2,0.5,0|4,2,0,2</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>24</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>神圣护盾</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F20" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>15</v>
+      </c>
+      <c r="I20" t="n">
+        <v>15</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>5,2,0,4</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>25</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>祝福</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F21" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>10</v>
+      </c>
+      <c r="I21" t="n">
+        <v>20</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>AllAlliesInRange</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>4,2,0,8</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>26</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>猛毒撕咬</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F22" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>5</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>SingleEnemy</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>1,1,1.0,0|4,1,0,1</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>27</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>寒冰吐息</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F23" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>8</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>AllEnemiesInRange</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>1,1,0.4,0|4,1,0,2</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>30</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>挑衅</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F24" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>8</v>
+      </c>
+      <c r="I24" t="n">
+        <v>5</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>SingleEnemy</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>1,1,0.5,0|4,1,0,9</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>31</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>燃烧</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F25" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H25" t="n">
+        <v>8</v>
+      </c>
+      <c r="I25" t="n">
+        <v>20</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>SingleEnemy</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>1,2,0.6,0|4,2,0,7</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>32</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>净化</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F26" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>8</v>
+      </c>
+      <c r="I26" t="n">
+        <v>10</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>6,2,0,0</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>33</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>狂暴</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F27" t="b">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H27" t="n">
+        <v>15</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>4,1,0,11</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
         <v>4</v>
       </c>
     </row>

--- a/tables/datas/common/#Skill-技能表.xlsx
+++ b/tables/datas/common/#Skill-技能表.xlsx
@@ -122,6 +122,37 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>System</author>
+  </authors>
+  <commentList>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>施法距离（格子数）
+0 = 自身/近身</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>目标类型（枚举）
+SingleEnemy = 单个敌人
+AllEnemiesInRange = 范围内所有敌人
+Self = 自身
+AllAlliesInRange = 范围内所有友方</t>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0">
+      <text>
+        <t>职业限制（common.EJobType 枚举）
+1=战士, 2=法师, 3=牧师, 4=刺客</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -526,7 +557,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>common.ESkillTargetType</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1588,5 +1619,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/tables/datas/common/#Skill-技能表.xlsx
+++ b/tables/datas/common/#Skill-技能表.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,6 +508,16 @@
           <t>job</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>projectile_speed</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>projectile_max_range</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -570,6 +580,16 @@
           <t>common.EJobType</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -630,6 +650,16 @@
       <c r="L3" t="inlineStr">
         <is>
           <t>所属职业</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>弹道速度(格/秒)</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>弹道最大距离(格)</t>
         </is>
       </c>
     </row>
@@ -790,11 +820,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1,2,1.5,0</t>
+          <t>7,2,1.5,0</t>
         </is>
       </c>
       <c r="L7" t="n">
         <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>5</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
